--- a/template_importacion_herramienta_facil.xlsx
+++ b/template_importacion_herramienta_facil.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contadoras" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validadores" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control_PPT" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partes_Criticas" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,8 +69,26 @@
       <color rgb="009E9E9E"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00FF9944"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0000FF88"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="008899AA"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -111,8 +130,33 @@
         <fgColor rgb="0016213E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A1F2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000D1117"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A2744"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E2535"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00161B27"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -134,11 +178,25 @@
         <color rgb="002A2A4A"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="002A3348"/>
+      </left>
+      <right style="thin">
+        <color rgb="002A3348"/>
+      </right>
+      <top style="thin">
+        <color rgb="002A3348"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="002A3348"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -165,6 +223,22 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -635,126 +709,323 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="inlineStr"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  📌  Partes_Criticas       → Pedidos de repuestos e insumos críticos</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>REGLAS IMPORTANTES:</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ✅  No borres la fila de encabezados (fila gris oscuro con texto verde)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✅  Las filas de EJEMPLO (en gris claro) sí se pueden borrar</t>
+          <t xml:space="preserve">  ✅  No borres la fila de encabezados (fila gris oscuro con texto verde)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✅  Las fechas deben tener el formato AAAA-MM-DD (ej: 2026-03-15)</t>
+          <t xml:space="preserve">  ✅  Las filas de EJEMPLO (en gris claro) sí se pueden borrar</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✅  Los campos marcados con * son OBLIGATORIOS</t>
+          <t xml:space="preserve">  ✅  Las fechas deben tener el formato AAAA-MM-DD (ej: 2026-03-15)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✅  Respetá exactamente los valores permitidos indicados en cada columna</t>
+          <t xml:space="preserve">  ✅  Los campos marcados con * son OBLIGATORIOS</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ✅  Respetá exactamente los valores permitidos indicados en cada columna</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ✅  Podés dejar hojas vacías — solo se importan las que tienen datos</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="inlineStr"/>
-    </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>VALORES FRECUENTES:</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Estado correctivos:    En Curso | Resuelto</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Estado preventivos:    Realizado | Pendiente</t>
+          <t xml:space="preserve">  Estado correctivos:    En Curso | Resuelto</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Estado tareas:         pendiente | en-curso | realizado</t>
+          <t xml:space="preserve">  Estado preventivos:    Realizado | Pendiente</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Prioridad tareas:      alta | media | baja</t>
+          <t xml:space="preserve">  Estado tareas:         pendiente | en-curso | realizado</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tipo EVA:              Correctivo | Preventivo</t>
+          <t xml:space="preserve">  Prioridad tareas:      alta | media | baja</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Estado EVA:            Pendiente | En Curso | Resuelto | Realizado</t>
+          <t xml:space="preserve">  Tipo EVA:              Correctivo | Preventivo</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tipo contadora:        Correctivo | Preventivo</t>
+          <t xml:space="preserve">  Estado EVA:            Pendiente | En Curso | Resuelto | Realizado</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Tipo contadora:        Correctivo | Preventivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Estado PPT:            PENDIENTE | REALIZADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Estado partes críticas:  Pendiente | En Tránsito | Recibido</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>🚨 PARTES CRÍTICAS — Pedidos de repuestos e insumos críticos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>⚠️  insumo* es OBLIGATORIO. estado: Pendiente | En Tránsito | Recibido. fechaPedido formato AAAA-MM-DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>insumo *</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>cantidad</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>fechaPedido</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>destino</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>isla</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>observaciones</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>estado *</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>fechaRecibido</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>insumo: nombre de la parte/repuesto. destino: N° pedido o remito. isla: isla afectada. fechaRecibido: solo si estado=Recibido (AAAA-MM-DD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Placa de monedas Aristocrat MK7</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>PC-0451</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Para isla 150, 2 máquinas fuera de servicio</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr"/>
+      <c r="I5" s="14" t="inlineStr"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Lector de billetes JCM WBA-23</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>PC-0452</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Recibido y ya instalado</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Recibido</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr"/>
+      <c r="B7" s="15" t="inlineStr"/>
+      <c r="C7" s="15" t="inlineStr"/>
+      <c r="D7" s="15" t="inlineStr"/>
+      <c r="E7" s="15" t="inlineStr"/>
+      <c r="F7" s="15" t="inlineStr"/>
+      <c r="G7" s="15" t="inlineStr"/>
+      <c r="H7" s="15" t="inlineStr"/>
+      <c r="I7" s="15" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
